--- a/resultados/Tabla1_Descriptivos.xlsx
+++ b/resultados/Tabla1_Descriptivos.xlsx
@@ -503,37 +503,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>50.21</v>
+        <v>54.11</v>
       </c>
       <c r="D4">
-        <v>16.01</v>
+        <v>15.02</v>
       </c>
       <c r="E4">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="F4">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="G4">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H4">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="I4">
-        <v>4.34</v>
+        <v>4.62</v>
       </c>
       <c r="J4">
-        <v>2.84</v>
+        <v>3.36</v>
       </c>
       <c r="K4">
-        <v>2.36</v>
+        <v>3.27</v>
       </c>
       <c r="L4">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="5">
